--- a/test.xlsx
+++ b/test.xlsx
@@ -44,7 +44,7 @@
     <t>到手价</t>
   </si>
   <si>
-    <t>ABAU019-31</t>
+    <t>ABAU037-1</t>
   </si>
   <si>
     <t>SOFT COOL 3</t>
